--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-moped-ext-neugeborenes.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
